--- a/Data layers/Important_locations.xlsx
+++ b/Data layers/Important_locations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\ArcGIS\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Data layers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41143BEC-BC87-46FD-99E9-20C6E77D0BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94CAB3E-C81E-4728-BF5E-AF4D933EB5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Longitude</t>
   </si>
@@ -66,19 +66,76 @@
   </si>
   <si>
     <t>Stuart</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Salinity logger</t>
+  </si>
+  <si>
+    <t>USGS-02323592</t>
+  </si>
+  <si>
+    <t>Flow logger</t>
+  </si>
+  <si>
+    <t>USGS-02310700</t>
+  </si>
+  <si>
+    <t>SSSal1</t>
+  </si>
+  <si>
+    <t>SSSal2</t>
+  </si>
+  <si>
+    <t>SSSal3</t>
+  </si>
+  <si>
+    <t>SSSal4</t>
+  </si>
+  <si>
+    <t>SSSal5</t>
+  </si>
+  <si>
+    <t>S49_S</t>
+  </si>
+  <si>
+    <t>S80_S</t>
+  </si>
+  <si>
+    <t>S97_S</t>
+  </si>
+  <si>
+    <t>HR1</t>
+  </si>
+  <si>
+    <t>STL_RIVER</t>
+  </si>
+  <si>
+    <t>STL-STPT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -101,8 +158,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA6A26-70AD-4971-B57D-DACA2AD4442C}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,8 +508,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>-82.720104000000006</v>
       </c>
@@ -461,8 +522,11 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>-83.142859999999999</v>
       </c>
@@ -472,8 +536,11 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>-83.377600000000001</v>
       </c>
@@ -483,8 +550,11 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-83.288775999999999</v>
       </c>
@@ -494,8 +564,11 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-83.034009999999995</v>
       </c>
@@ -505,8 +578,11 @@
       <c r="C6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-82.621020000000001</v>
       </c>
@@ -516,8 +592,11 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-80.254469999999998</v>
       </c>
@@ -526,6 +605,191 @@
       </c>
       <c r="C8" t="s">
         <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>-83.086667000000006</v>
+      </c>
+      <c r="B9">
+        <v>29.339167</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>-82.617926267019001</v>
+      </c>
+      <c r="B10" s="1">
+        <v>28.785277047241902</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>-83.162099999999995</v>
+      </c>
+      <c r="B11">
+        <v>29.299849999999999</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>-83.062749999999994</v>
+      </c>
+      <c r="B12">
+        <v>29.15558</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>-83.241699999999994</v>
+      </c>
+      <c r="B13">
+        <v>29.3917</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>-83.341700000000003</v>
+      </c>
+      <c r="B14">
+        <v>29.441700000000001</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>-83.022779999999997</v>
+      </c>
+      <c r="B15">
+        <v>29.399170000000002</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>-80.359804999999994</v>
+      </c>
+      <c r="B16">
+        <v>27.261393000000002</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>-80.285263</v>
+      </c>
+      <c r="B17">
+        <v>27.111789000000002</v>
+      </c>
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>-80.34066</v>
+      </c>
+      <c r="B18">
+        <v>27.205549000000001</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>-80.288118999999995</v>
+      </c>
+      <c r="B19">
+        <v>27.22814</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>-80.258364</v>
+      </c>
+      <c r="B20">
+        <v>27.201958000000001</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>-80.207002000000003</v>
+      </c>
+      <c r="B21">
+        <v>27.199384999999999</v>
+      </c>
+      <c r="C21" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Data layers/Important_locations.xlsx
+++ b/Data layers/Important_locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Data layers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94CAB3E-C81E-4728-BF5E-AF4D933EB5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F68B8B-0787-415B-9FA6-6356E7C9D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
+    <workbookView xWindow="1632" yWindow="2820" windowWidth="17280" windowHeight="8928" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Longitude</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>STL-STPT</t>
+  </si>
+  <si>
+    <t>USGS-02313700</t>
   </si>
 </sst>
 </file>
@@ -495,10 +498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA6A26-70AD-4971-B57D-DACA2AD4442C}">
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,7 +519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>-82.720104000000006</v>
       </c>
@@ -526,7 +533,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>-83.142859999999999</v>
       </c>
@@ -540,7 +547,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>-83.377600000000001</v>
       </c>
@@ -554,7 +561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>-83.288775999999999</v>
       </c>
@@ -568,7 +575,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-83.034009999999995</v>
       </c>
@@ -582,7 +589,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>-82.621020000000001</v>
       </c>
@@ -596,7 +603,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>-80.254469999999998</v>
       </c>
@@ -610,7 +617,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>-83.086667000000006</v>
       </c>
@@ -624,7 +631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>-82.617926267019001</v>
       </c>
@@ -638,7 +645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>-83.162099999999995</v>
       </c>
@@ -652,7 +659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>-83.062749999999994</v>
       </c>
@@ -666,7 +673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>-83.241699999999994</v>
       </c>
@@ -680,7 +687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>-83.341700000000003</v>
       </c>
@@ -694,7 +701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>-83.022779999999997</v>
       </c>
@@ -708,7 +715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>-80.359804999999994</v>
       </c>
@@ -722,7 +729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>-80.285263</v>
       </c>
@@ -736,7 +743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>-80.34066</v>
       </c>
@@ -750,7 +757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>-80.288118999999995</v>
       </c>
@@ -764,7 +771,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>-80.258364</v>
       </c>
@@ -778,7 +785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>-80.207002000000003</v>
       </c>
@@ -790,6 +797,20 @@
       </c>
       <c r="D21" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>-82.769001071597003</v>
+      </c>
+      <c r="B22" s="1">
+        <v>29.204133775691599</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Data layers/Important_locations.xlsx
+++ b/Data layers/Important_locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Data layers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F68B8B-0787-415B-9FA6-6356E7C9D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5850796-63F0-48ED-A33D-F31DB488F713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1632" yWindow="2820" windowWidth="17280" windowHeight="8928" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>Longitude</t>
   </si>
@@ -120,6 +120,54 @@
   </si>
   <si>
     <t>USGS-02313700</t>
+  </si>
+  <si>
+    <t>WISal1</t>
+  </si>
+  <si>
+    <t>WISal2</t>
+  </si>
+  <si>
+    <t>WISal3</t>
+  </si>
+  <si>
+    <t>WISal4</t>
+  </si>
+  <si>
+    <t>WISal5</t>
+  </si>
+  <si>
+    <t>WISal6</t>
+  </si>
+  <si>
+    <t>USGS-02313272</t>
+  </si>
+  <si>
+    <t>USGS-285447082445100</t>
+  </si>
+  <si>
+    <t>USGS-285531082412600</t>
+  </si>
+  <si>
+    <t>USGS-02310712</t>
+  </si>
+  <si>
+    <t>USGS-284506082435801</t>
+  </si>
+  <si>
+    <t>USGS-02310752</t>
+  </si>
+  <si>
+    <t>USGS-02313250</t>
+  </si>
+  <si>
+    <t>USGS-02310750</t>
+  </si>
+  <si>
+    <t>USGS-02313230</t>
+  </si>
+  <si>
+    <t>Crystal River</t>
   </si>
 </sst>
 </file>
@@ -498,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA6A26-70AD-4971-B57D-DACA2AD4442C}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -813,6 +861,300 @@
         <v>14</v>
       </c>
     </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>-82.641480000000001</v>
+      </c>
+      <c r="B23">
+        <v>28.90296</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>-82.765829999999994</v>
+      </c>
+      <c r="B24">
+        <v>29.00113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>-82.769000000000005</v>
+      </c>
+      <c r="B25">
+        <v>29.204129999999999</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>-82.690640000000002</v>
+      </c>
+      <c r="B26">
+        <v>28.925280000000001</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>-82.747640000000004</v>
+      </c>
+      <c r="B27">
+        <v>28.91169</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>-82.732889999999998</v>
+      </c>
+      <c r="B28">
+        <v>28.751580000000001</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>-82.769001071597003</v>
+      </c>
+      <c r="B29">
+        <v>29.204133775691599</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>-82.769001071597003</v>
+      </c>
+      <c r="B30">
+        <v>29.204133775691599</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>-82.765833008482403</v>
+      </c>
+      <c r="B31">
+        <v>29.001128728537498</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>-82.747638888888801</v>
+      </c>
+      <c r="B32">
+        <v>28.911691666666599</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>-82.690638888888898</v>
+      </c>
+      <c r="B33">
+        <v>28.925277777777801</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>-82.695706281747107</v>
+      </c>
+      <c r="B34">
+        <v>28.7716664406531</v>
+      </c>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>-82.732891666666603</v>
+      </c>
+      <c r="B35">
+        <v>28.751583333333301</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>-82.645805555555498</v>
+      </c>
+      <c r="B36">
+        <v>28.9015555555555</v>
+      </c>
+      <c r="C36" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>-82.637881756271497</v>
+      </c>
+      <c r="B37">
+        <v>29.0210853789327</v>
+      </c>
+      <c r="C37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>-82.635188270857199</v>
+      </c>
+      <c r="B38">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>-82.635188270857199</v>
+      </c>
+      <c r="B39">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>-82.616769865935098</v>
+      </c>
+      <c r="B40">
+        <v>29.0099748538913</v>
+      </c>
+      <c r="C40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>-82.617926267019001</v>
+      </c>
+      <c r="B41">
+        <v>28.785277047241902</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>-82.617926267019001</v>
+      </c>
+      <c r="B42">
+        <v>28.785277047241902</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>-82.633741999999998</v>
+      </c>
+      <c r="B43">
+        <v>28.899311999999998</v>
+      </c>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data layers/Important_locations.xlsx
+++ b/Data layers/Important_locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Data layers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F68B8B-0787-415B-9FA6-6356E7C9D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA66B6FD-E697-4250-8F89-04F19C7C0F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1632" yWindow="2820" windowWidth="17280" windowHeight="8928" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="68">
   <si>
     <t>Longitude</t>
   </si>
@@ -120,6 +120,126 @@
   </si>
   <si>
     <t>USGS-02313700</t>
+  </si>
+  <si>
+    <t>Pensacola</t>
+  </si>
+  <si>
+    <t>Destin</t>
+  </si>
+  <si>
+    <t>Milton</t>
+  </si>
+  <si>
+    <t>USGS-02369600</t>
+  </si>
+  <si>
+    <t>USGS-02370140</t>
+  </si>
+  <si>
+    <t>USGS-02370500</t>
+  </si>
+  <si>
+    <t>USGS-02376033</t>
+  </si>
+  <si>
+    <t>USGS-02376115</t>
+  </si>
+  <si>
+    <t>USGS-02377750</t>
+  </si>
+  <si>
+    <t>PESal1</t>
+  </si>
+  <si>
+    <t>PESal10</t>
+  </si>
+  <si>
+    <t>PESal11</t>
+  </si>
+  <si>
+    <t>PESal12</t>
+  </si>
+  <si>
+    <t>PESal13</t>
+  </si>
+  <si>
+    <t>PESal14</t>
+  </si>
+  <si>
+    <t>PESal15</t>
+  </si>
+  <si>
+    <t>PESal16</t>
+  </si>
+  <si>
+    <t>PESal17</t>
+  </si>
+  <si>
+    <t>PESal18</t>
+  </si>
+  <si>
+    <t>PESal19</t>
+  </si>
+  <si>
+    <t>PESal2</t>
+  </si>
+  <si>
+    <t>PESal20</t>
+  </si>
+  <si>
+    <t>PESal21</t>
+  </si>
+  <si>
+    <t>PESal22</t>
+  </si>
+  <si>
+    <t>PESal23</t>
+  </si>
+  <si>
+    <t>PESal24</t>
+  </si>
+  <si>
+    <t>PESal25</t>
+  </si>
+  <si>
+    <t>PESal26</t>
+  </si>
+  <si>
+    <t>PESal27</t>
+  </si>
+  <si>
+    <t>PESal28</t>
+  </si>
+  <si>
+    <t>PESal29</t>
+  </si>
+  <si>
+    <t>PESal3</t>
+  </si>
+  <si>
+    <t>PESal30</t>
+  </si>
+  <si>
+    <t>PESal31</t>
+  </si>
+  <si>
+    <t>PESal4</t>
+  </si>
+  <si>
+    <t>PESal5</t>
+  </si>
+  <si>
+    <t>PESal6</t>
+  </si>
+  <si>
+    <t>PESal7</t>
+  </si>
+  <si>
+    <t>PESal8</t>
+  </si>
+  <si>
+    <t>PESal9</t>
   </si>
 </sst>
 </file>
@@ -498,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA6A26-70AD-4971-B57D-DACA2AD4442C}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -813,6 +933,566 @@
         <v>14</v>
       </c>
     </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>-87.218414999999993</v>
+      </c>
+      <c r="B23">
+        <v>30.403119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>-86.503625999999997</v>
+      </c>
+      <c r="B24">
+        <v>30.381924000000001</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>-87.040513000000004</v>
+      </c>
+      <c r="B25">
+        <v>30.625382999999999</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>-86.923573249692595</v>
+      </c>
+      <c r="B26">
+        <v>30.569639010468102</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>-86.881721999999996</v>
+      </c>
+      <c r="B27">
+        <v>30.704722</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>-86.972186008971605</v>
+      </c>
+      <c r="B28">
+        <v>30.708523747278601</v>
+      </c>
+      <c r="C28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>-87.266917872714899</v>
+      </c>
+      <c r="B29">
+        <v>30.6701917020841</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>-87.3358086143744</v>
+      </c>
+      <c r="B30">
+        <v>30.498251588581201</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>-87.462757747521806</v>
+      </c>
+      <c r="B31">
+        <v>30.518250888523401</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>-87.152010000000004</v>
+      </c>
+      <c r="B32">
+        <v>30.33436</v>
+      </c>
+      <c r="C32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>-87.085809999999995</v>
+      </c>
+      <c r="B33">
+        <v>30.375689999999999</v>
+      </c>
+      <c r="C33" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>-87.174639999999997</v>
+      </c>
+      <c r="B34">
+        <v>30.593830000000001</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>-86.885660000000001</v>
+      </c>
+      <c r="B35">
+        <v>30.399280000000001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>-87.122</v>
+      </c>
+      <c r="B36">
+        <v>30.466830000000002</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>-87.159000000000006</v>
+      </c>
+      <c r="B37">
+        <v>30.400500000000001</v>
+      </c>
+      <c r="C37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>-87.054329999999993</v>
+      </c>
+      <c r="B38">
+        <v>30.427499999999998</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>-86.990359999999995</v>
+      </c>
+      <c r="B39">
+        <v>30.386279999999999</v>
+      </c>
+      <c r="C39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>-86.945310000000006</v>
+      </c>
+      <c r="B40">
+        <v>30.386240000000001</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>-87.338080000000005</v>
+      </c>
+      <c r="B41">
+        <v>30.453279999999999</v>
+      </c>
+      <c r="C41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>-86.619810000000001</v>
+      </c>
+      <c r="B42">
+        <v>30.419450000000001</v>
+      </c>
+      <c r="C42" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>-87.276210000000006</v>
+      </c>
+      <c r="B43">
+        <v>30.394749999999998</v>
+      </c>
+      <c r="C43" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>-87.248109999999997</v>
+      </c>
+      <c r="B44">
+        <v>30.564769999999999</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>-87.334580000000003</v>
+      </c>
+      <c r="B45">
+        <v>30.502669999999998</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>-87.320369999999997</v>
+      </c>
+      <c r="B46">
+        <v>30.54898</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>-87.349199999999996</v>
+      </c>
+      <c r="B47">
+        <v>30.3673</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>-87.412090000000006</v>
+      </c>
+      <c r="B48">
+        <v>30.351849999999999</v>
+      </c>
+      <c r="C48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>-87.40316</v>
+      </c>
+      <c r="B49">
+        <v>30.572150000000001</v>
+      </c>
+      <c r="C49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>-86.936040000000006</v>
+      </c>
+      <c r="B50">
+        <v>30.433979999999998</v>
+      </c>
+      <c r="C50" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>-87.059340000000006</v>
+      </c>
+      <c r="B51">
+        <v>30.606739999999999</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>-86.900170000000003</v>
+      </c>
+      <c r="B52">
+        <v>30.578949999999999</v>
+      </c>
+      <c r="C52" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>-86.930629999999994</v>
+      </c>
+      <c r="B53">
+        <v>30.577839999999998</v>
+      </c>
+      <c r="C53" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>-87.151340000000005</v>
+      </c>
+      <c r="B54">
+        <v>30.522189999999998</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>-86.853759999999994</v>
+      </c>
+      <c r="B55">
+        <v>30.619319999999998</v>
+      </c>
+      <c r="C55" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>-87.426500000000004</v>
+      </c>
+      <c r="B56">
+        <v>30.4023</v>
+      </c>
+      <c r="C56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>-87.207920000000001</v>
+      </c>
+      <c r="B57">
+        <v>30.454989999999999</v>
+      </c>
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>-87.221119999999999</v>
+      </c>
+      <c r="B58">
+        <v>30.550640000000001</v>
+      </c>
+      <c r="C58" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>-86.866510000000005</v>
+      </c>
+      <c r="B59">
+        <v>30.440079999999998</v>
+      </c>
+      <c r="C59" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>-87.03528</v>
+      </c>
+      <c r="B60">
+        <v>30.622309999999999</v>
+      </c>
+      <c r="C60" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>-86.90558</v>
+      </c>
+      <c r="B61">
+        <v>30.451519999999999</v>
+      </c>
+      <c r="C61" t="s">
+        <v>66</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>-87.029880000000006</v>
+      </c>
+      <c r="B62">
+        <v>30.537120000000002</v>
+      </c>
+      <c r="C62" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data layers/Important_locations.xlsx
+++ b/Data layers/Important_locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Data layers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5850796-63F0-48ED-A33D-F31DB488F713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45507833-2A01-4BC0-9D5C-A3191C89FD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{2CA14E8E-9857-4D7B-B94E-961384FE881B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="67">
   <si>
     <t>Longitude</t>
   </si>
@@ -168,6 +168,75 @@
   </si>
   <si>
     <t>Crystal River</t>
+  </si>
+  <si>
+    <t>Panama City</t>
+  </si>
+  <si>
+    <t>Panama City Beach</t>
+  </si>
+  <si>
+    <t>USGS-02359500</t>
+  </si>
+  <si>
+    <t>USGS-295308085143700</t>
+  </si>
+  <si>
+    <t>USGS-295323085151700</t>
+  </si>
+  <si>
+    <t>USGS-301116085443000</t>
+  </si>
+  <si>
+    <t>SASal1</t>
+  </si>
+  <si>
+    <t>SASal10</t>
+  </si>
+  <si>
+    <t>SASal11</t>
+  </si>
+  <si>
+    <t>SASal12</t>
+  </si>
+  <si>
+    <t>SASal13</t>
+  </si>
+  <si>
+    <t>SASal14</t>
+  </si>
+  <si>
+    <t>SASal15</t>
+  </si>
+  <si>
+    <t>SASal16</t>
+  </si>
+  <si>
+    <t>SASal17</t>
+  </si>
+  <si>
+    <t>SASal2</t>
+  </si>
+  <si>
+    <t>SASal3</t>
+  </si>
+  <si>
+    <t>SASal4</t>
+  </si>
+  <si>
+    <t>SASal5</t>
+  </si>
+  <si>
+    <t>SASal6</t>
+  </si>
+  <si>
+    <t>SASal7</t>
+  </si>
+  <si>
+    <t>SASal8</t>
+  </si>
+  <si>
+    <t>SASal9</t>
   </si>
 </sst>
 </file>
@@ -546,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA6A26-70AD-4971-B57D-DACA2AD4442C}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1155,6 +1224,328 @@
         <v>11</v>
       </c>
     </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>-85.664229777418797</v>
+      </c>
+      <c r="B44">
+        <v>30.173205209170899</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>-85.893749739127401</v>
+      </c>
+      <c r="B45">
+        <v>30.227494626507799</v>
+      </c>
+      <c r="C45" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>-85.556593228370701</v>
+      </c>
+      <c r="B46">
+        <v>30.384640616919</v>
+      </c>
+      <c r="C46" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>-85.243611111111093</v>
+      </c>
+      <c r="B47">
+        <v>29.885555555555602</v>
+      </c>
+      <c r="C47" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>-85.254722222222199</v>
+      </c>
+      <c r="B48">
+        <v>29.889722222222201</v>
+      </c>
+      <c r="C48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>-85.741666666666703</v>
+      </c>
+      <c r="B49">
+        <v>30.187833333333302</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>-85.689719999999994</v>
+      </c>
+      <c r="B50">
+        <v>30.228179999999998</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>-85.602130000000002</v>
+      </c>
+      <c r="B51">
+        <v>30.13072</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>-85.738259999999997</v>
+      </c>
+      <c r="B52">
+        <v>30.275510000000001</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>-85.741669999999999</v>
+      </c>
+      <c r="B53">
+        <v>30.175000000000001</v>
+      </c>
+      <c r="C53" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>-85.402699999999996</v>
+      </c>
+      <c r="B54">
+        <v>30.053699999999999</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>-85.437420000000003</v>
+      </c>
+      <c r="B55">
+        <v>30.062830000000002</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>-85.500330000000005</v>
+      </c>
+      <c r="B56">
+        <v>30.07733</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>-85.440330000000003</v>
+      </c>
+      <c r="B57">
+        <v>30.036000000000001</v>
+      </c>
+      <c r="C57" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>-85.598320000000001</v>
+      </c>
+      <c r="B58">
+        <v>30.234729999999999</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>-85.763329999999996</v>
+      </c>
+      <c r="B59">
+        <v>30.295670000000001</v>
+      </c>
+      <c r="C59" t="s">
+        <v>59</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>-85.564130000000006</v>
+      </c>
+      <c r="B60">
+        <v>30.125499999999999</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>-85.806920000000005</v>
+      </c>
+      <c r="B61">
+        <v>30.278210000000001</v>
+      </c>
+      <c r="C61" t="s">
+        <v>61</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>-85.486670000000004</v>
+      </c>
+      <c r="B62">
+        <v>30.038329999999998</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>-85.651880000000006</v>
+      </c>
+      <c r="B63">
+        <v>30.146529999999998</v>
+      </c>
+      <c r="C63" t="s">
+        <v>63</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>-85.779949999999999</v>
+      </c>
+      <c r="B64">
+        <v>30.165679999999998</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>-85.733680000000007</v>
+      </c>
+      <c r="B65">
+        <v>30.13129</v>
+      </c>
+      <c r="C65" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>-85.518119999999996</v>
+      </c>
+      <c r="B66">
+        <v>30.126380000000001</v>
+      </c>
+      <c r="C66" t="s">
+        <v>66</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
